--- a/artfynd/A 23587-2025 artfynd.xlsx
+++ b/artfynd/A 23587-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1303,6 +1303,501 @@
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>126022890</v>
+      </c>
+      <c r="B7" t="n">
+        <v>91521</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>658</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Rhodofomes roseus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Hällesjö, Jmt</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>556582</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6972362</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>126022888</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57648</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Hällesjö, Jmt</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>556630</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6972255</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Födosöksspår</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>126022885</v>
+      </c>
+      <c r="B9" t="n">
+        <v>56843</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Hällesjö, Jmt</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>556630</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6972265</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Hane</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>126022895</v>
+      </c>
+      <c r="B10" t="n">
+        <v>97210</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Hällesjö, Jmt</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>556585</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6972326</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>126022891</v>
+      </c>
+      <c r="B11" t="n">
+        <v>91521</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>658</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Rhodofomes roseus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Hällesjö, Jmt</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>556639</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6972253</v>
+      </c>
+      <c r="S11" t="n">
+        <v>25</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 23587-2025 artfynd.xlsx
+++ b/artfynd/A 23587-2025 artfynd.xlsx
@@ -1308,7 +1308,7 @@
         <v>126022890</v>
       </c>
       <c r="B7" t="n">
-        <v>91521</v>
+        <v>91524</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1606,32 +1606,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126022895</v>
+        <v>126022891</v>
       </c>
       <c r="B10" t="n">
-        <v>97210</v>
+        <v>91524</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221945</v>
+        <v>658</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1641,10 +1641,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>556585</v>
+        <v>556639</v>
       </c>
       <c r="R10" t="n">
-        <v>6972326</v>
+        <v>6972253</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1703,32 +1703,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126022891</v>
+        <v>126022895</v>
       </c>
       <c r="B11" t="n">
-        <v>91521</v>
+        <v>97212</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>658</v>
+        <v>221945</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1738,10 +1738,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>556639</v>
+        <v>556585</v>
       </c>
       <c r="R11" t="n">
-        <v>6972253</v>
+        <v>6972326</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>

--- a/artfynd/A 23587-2025 artfynd.xlsx
+++ b/artfynd/A 23587-2025 artfynd.xlsx
@@ -1308,7 +1308,7 @@
         <v>126022890</v>
       </c>
       <c r="B7" t="n">
-        <v>91524</v>
+        <v>91528</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1609,7 +1609,7 @@
         <v>126022891</v>
       </c>
       <c r="B10" t="n">
-        <v>91524</v>
+        <v>91528</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1706,7 +1706,7 @@
         <v>126022895</v>
       </c>
       <c r="B11" t="n">
-        <v>97212</v>
+        <v>97216</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 23587-2025 artfynd.xlsx
+++ b/artfynd/A 23587-2025 artfynd.xlsx
@@ -1706,7 +1706,7 @@
         <v>126022895</v>
       </c>
       <c r="B11" t="n">
-        <v>97216</v>
+        <v>97217</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 23587-2025 artfynd.xlsx
+++ b/artfynd/A 23587-2025 artfynd.xlsx
@@ -1606,32 +1606,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126022891</v>
+        <v>126022895</v>
       </c>
       <c r="B10" t="n">
-        <v>91528</v>
+        <v>97217</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>658</v>
+        <v>221945</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1641,10 +1641,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>556639</v>
+        <v>556585</v>
       </c>
       <c r="R10" t="n">
-        <v>6972253</v>
+        <v>6972326</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1703,32 +1703,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126022895</v>
+        <v>126022891</v>
       </c>
       <c r="B11" t="n">
-        <v>97217</v>
+        <v>91528</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221945</v>
+        <v>658</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1738,10 +1738,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>556585</v>
+        <v>556639</v>
       </c>
       <c r="R11" t="n">
-        <v>6972326</v>
+        <v>6972253</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>

--- a/artfynd/A 23587-2025 artfynd.xlsx
+++ b/artfynd/A 23587-2025 artfynd.xlsx
@@ -1606,32 +1606,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126022895</v>
+        <v>126022891</v>
       </c>
       <c r="B10" t="n">
-        <v>97217</v>
+        <v>91528</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221945</v>
+        <v>658</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1641,10 +1641,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>556585</v>
+        <v>556639</v>
       </c>
       <c r="R10" t="n">
-        <v>6972326</v>
+        <v>6972253</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1703,32 +1703,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126022891</v>
+        <v>126022895</v>
       </c>
       <c r="B11" t="n">
-        <v>91528</v>
+        <v>97217</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>658</v>
+        <v>221945</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1738,10 +1738,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>556639</v>
+        <v>556585</v>
       </c>
       <c r="R11" t="n">
-        <v>6972253</v>
+        <v>6972326</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>

--- a/artfynd/A 23587-2025 artfynd.xlsx
+++ b/artfynd/A 23587-2025 artfynd.xlsx
@@ -1308,7 +1308,7 @@
         <v>126022890</v>
       </c>
       <c r="B7" t="n">
-        <v>91528</v>
+        <v>91530</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1405,7 +1405,7 @@
         <v>126022888</v>
       </c>
       <c r="B8" t="n">
-        <v>57648</v>
+        <v>57649</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1507,7 +1507,7 @@
         <v>126022885</v>
       </c>
       <c r="B9" t="n">
-        <v>56843</v>
+        <v>56844</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1609,7 +1609,7 @@
         <v>126022891</v>
       </c>
       <c r="B10" t="n">
-        <v>91528</v>
+        <v>91530</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1706,7 +1706,7 @@
         <v>126022895</v>
       </c>
       <c r="B11" t="n">
-        <v>97217</v>
+        <v>97219</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 23587-2025 artfynd.xlsx
+++ b/artfynd/A 23587-2025 artfynd.xlsx
@@ -1308,7 +1308,7 @@
         <v>126022890</v>
       </c>
       <c r="B7" t="n">
-        <v>91530</v>
+        <v>91532</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1609,7 +1609,7 @@
         <v>126022891</v>
       </c>
       <c r="B10" t="n">
-        <v>91530</v>
+        <v>91532</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1706,7 +1706,7 @@
         <v>126022895</v>
       </c>
       <c r="B11" t="n">
-        <v>97219</v>
+        <v>97221</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 23587-2025 artfynd.xlsx
+++ b/artfynd/A 23587-2025 artfynd.xlsx
@@ -1308,7 +1308,7 @@
         <v>126022890</v>
       </c>
       <c r="B7" t="n">
-        <v>91532</v>
+        <v>91534</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1609,7 +1609,7 @@
         <v>126022891</v>
       </c>
       <c r="B10" t="n">
-        <v>91532</v>
+        <v>91534</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1706,7 +1706,7 @@
         <v>126022895</v>
       </c>
       <c r="B11" t="n">
-        <v>97221</v>
+        <v>97223</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 23587-2025 artfynd.xlsx
+++ b/artfynd/A 23587-2025 artfynd.xlsx
@@ -1308,7 +1308,7 @@
         <v>126022890</v>
       </c>
       <c r="B7" t="n">
-        <v>91534</v>
+        <v>91538</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1405,7 +1405,7 @@
         <v>126022888</v>
       </c>
       <c r="B8" t="n">
-        <v>57649</v>
+        <v>57653</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1507,7 +1507,7 @@
         <v>126022885</v>
       </c>
       <c r="B9" t="n">
-        <v>56844</v>
+        <v>56848</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1609,7 +1609,7 @@
         <v>126022891</v>
       </c>
       <c r="B10" t="n">
-        <v>91534</v>
+        <v>91538</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1706,7 +1706,7 @@
         <v>126022895</v>
       </c>
       <c r="B11" t="n">
-        <v>97223</v>
+        <v>97227</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 23587-2025 artfynd.xlsx
+++ b/artfynd/A 23587-2025 artfynd.xlsx
@@ -1606,32 +1606,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126022891</v>
+        <v>126022895</v>
       </c>
       <c r="B10" t="n">
-        <v>91538</v>
+        <v>97230</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>658</v>
+        <v>221945</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1641,10 +1641,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>556639</v>
+        <v>556585</v>
       </c>
       <c r="R10" t="n">
-        <v>6972253</v>
+        <v>6972326</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1703,32 +1703,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126022895</v>
+        <v>126022891</v>
       </c>
       <c r="B11" t="n">
-        <v>97227</v>
+        <v>91538</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221945</v>
+        <v>658</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1738,10 +1738,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>556585</v>
+        <v>556639</v>
       </c>
       <c r="R11" t="n">
-        <v>6972326</v>
+        <v>6972253</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>

--- a/artfynd/A 23587-2025 artfynd.xlsx
+++ b/artfynd/A 23587-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1606,32 +1606,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126022895</v>
+        <v>126022891</v>
       </c>
       <c r="B10" t="n">
-        <v>97230</v>
+        <v>91538</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221945</v>
+        <v>658</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1641,10 +1641,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>556585</v>
+        <v>556639</v>
       </c>
       <c r="R10" t="n">
-        <v>6972326</v>
+        <v>6972253</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1703,32 +1703,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126022891</v>
+        <v>126022895</v>
       </c>
       <c r="B11" t="n">
-        <v>91538</v>
+        <v>97230</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>658</v>
+        <v>221945</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1738,10 +1738,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>556639</v>
+        <v>556585</v>
       </c>
       <c r="R11" t="n">
-        <v>6972253</v>
+        <v>6972326</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1797,6 +1797,116 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>126421047</v>
+      </c>
+      <c r="B12" t="n">
+        <v>57656</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Brantbergtjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>556674</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6972415</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Bohål 2,5m upp i gran med grantickor</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 23587-2025 artfynd.xlsx
+++ b/artfynd/A 23587-2025 artfynd.xlsx
@@ -1308,7 +1308,7 @@
         <v>126022890</v>
       </c>
       <c r="B7" t="n">
-        <v>91538</v>
+        <v>91541</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1405,7 +1405,7 @@
         <v>126022888</v>
       </c>
       <c r="B8" t="n">
-        <v>57653</v>
+        <v>57654</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1507,7 +1507,7 @@
         <v>126022885</v>
       </c>
       <c r="B9" t="n">
-        <v>56848</v>
+        <v>56849</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1609,7 +1609,7 @@
         <v>126022891</v>
       </c>
       <c r="B10" t="n">
-        <v>91538</v>
+        <v>91541</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1706,7 +1706,7 @@
         <v>126022895</v>
       </c>
       <c r="B11" t="n">
-        <v>97230</v>
+        <v>97239</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>126421047</v>
       </c>
       <c r="B12" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 23587-2025 artfynd.xlsx
+++ b/artfynd/A 23587-2025 artfynd.xlsx
@@ -1606,32 +1606,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126022891</v>
+        <v>126022895</v>
       </c>
       <c r="B10" t="n">
-        <v>91541</v>
+        <v>97239</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>658</v>
+        <v>221945</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1641,10 +1641,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>556639</v>
+        <v>556585</v>
       </c>
       <c r="R10" t="n">
-        <v>6972253</v>
+        <v>6972326</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1703,32 +1703,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126022895</v>
+        <v>126022891</v>
       </c>
       <c r="B11" t="n">
-        <v>97239</v>
+        <v>91541</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221945</v>
+        <v>658</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1738,10 +1738,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>556585</v>
+        <v>556639</v>
       </c>
       <c r="R11" t="n">
-        <v>6972326</v>
+        <v>6972253</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>

--- a/artfynd/A 23587-2025 artfynd.xlsx
+++ b/artfynd/A 23587-2025 artfynd.xlsx
@@ -1606,32 +1606,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126022895</v>
+        <v>126022891</v>
       </c>
       <c r="B10" t="n">
-        <v>97239</v>
+        <v>91541</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221945</v>
+        <v>658</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1641,10 +1641,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>556585</v>
+        <v>556639</v>
       </c>
       <c r="R10" t="n">
-        <v>6972326</v>
+        <v>6972253</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1703,32 +1703,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126022891</v>
+        <v>126022895</v>
       </c>
       <c r="B11" t="n">
-        <v>91541</v>
+        <v>97239</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>658</v>
+        <v>221945</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1738,10 +1738,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>556639</v>
+        <v>556585</v>
       </c>
       <c r="R11" t="n">
-        <v>6972253</v>
+        <v>6972326</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>

--- a/artfynd/A 23587-2025 artfynd.xlsx
+++ b/artfynd/A 23587-2025 artfynd.xlsx
@@ -1803,7 +1803,7 @@
         <v>126421047</v>
       </c>
       <c r="B12" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 23587-2025 artfynd.xlsx
+++ b/artfynd/A 23587-2025 artfynd.xlsx
@@ -1803,7 +1803,7 @@
         <v>126421047</v>
       </c>
       <c r="B12" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 23587-2025 artfynd.xlsx
+++ b/artfynd/A 23587-2025 artfynd.xlsx
@@ -1803,7 +1803,7 @@
         <v>126421047</v>
       </c>
       <c r="B12" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 23587-2025 artfynd.xlsx
+++ b/artfynd/A 23587-2025 artfynd.xlsx
@@ -1803,7 +1803,7 @@
         <v>126421047</v>
       </c>
       <c r="B12" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
